--- a/artfynd/A 4087-2025 artfynd.xlsx
+++ b/artfynd/A 4087-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>86586036</v>
       </c>
       <c r="B2" t="n">
-        <v>99566</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>102419</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529633.495933805</v>
+        <v>529633</v>
       </c>
       <c r="R2" t="n">
-        <v>6502443.510186414</v>
+        <v>6502444</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -752,19 +747,9 @@
           <t>2020-06-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-06-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,6 +774,108 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>86586012</v>
+      </c>
+      <c r="B3" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kålhagsgölen 200 m N, Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>529640</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6502212</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hällestad</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2020-06-24</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2020-06-24</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Björn Ström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Björn Ström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
